--- a/channeltalk-customer-profile-fields.xlsx
+++ b/channeltalk-customer-profile-fields.xlsx
@@ -12,7 +12,7 @@
     <sheet name="요약" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'고객 프로필 정보'!$A$1:$G$53</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'고객 프로필 정보'!$A$1:$H$53</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="138">
   <si>
     <t xml:space="preserve">No.</t>
   </si>
@@ -47,6 +47,9 @@
     <t xml:space="preserve">동기화</t>
   </si>
   <si>
+    <t xml:space="preserve">수정 가능</t>
+  </si>
+  <si>
     <t xml:space="preserve">기본 프로필</t>
   </si>
   <si>
@@ -63,6 +66,9 @@
   </si>
   <si>
     <t xml:space="preserve">-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O</t>
   </si>
   <si>
     <t xml:space="preserve">profile.email</t>
@@ -1011,6 +1017,132 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF667085"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">수정 가능</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF667085"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(O) = </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF667085"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">화면 우측에 수정</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF667085"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF667085"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">연필</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF667085"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF667085"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">버튼이 있는 필드로</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF667085"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, profile.* </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF667085"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">커스텀 필드 </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF667085"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF667085"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개가 해당됨</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF667085"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">.</t>
     </r>
   </si>
@@ -1025,6 +1157,44 @@
   </si>
   <si>
     <t xml:space="preserve">분류별 필드 수</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">수정 가능 필드 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(O)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">수정 불가 필드 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(-)</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -1034,7 +1204,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1082,6 +1252,14 @@
       <sz val="10"/>
       <name val="WenQuanYi Zen Hei"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF1570EF"/>
+      <name val="Malgun Gothic"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <i val="true"/>
@@ -1174,7 +1352,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1199,6 +1377,10 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1211,11 +1393,15 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1240,7 +1426,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="5">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1272,6 +1458,14 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF1570EF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <colors>
     <indexedColors>
@@ -1297,7 +1491,7 @@
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FF1570EF"/>
       <rgbColor rgb="FFD0D5DD"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
@@ -1520,7 +1714,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:H55"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
@@ -1530,6 +1724,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="10"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1554,28 +1749,34 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1583,22 +1784,25 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="6" t="s">
         <v>14</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1606,22 +1810,25 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1629,22 +1836,25 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1652,22 +1862,25 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1675,22 +1888,25 @@
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1698,91 +1914,103 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" s="7" t="s">
+      <c r="B11" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E9" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>12</v>
+      <c r="C11" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1790,22 +2018,25 @@
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1813,114 +2044,129 @@
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D13" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E13" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E13" s="3" t="s">
-        <v>36</v>
-      </c>
       <c r="F13" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="D14" s="7" t="s">
+      <c r="A14" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="C14" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="F14" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>12</v>
+      <c r="D14" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="n">
+      <c r="A15" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="D15" s="7" t="s">
+      <c r="B15" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="E16" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="E15" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>12</v>
+      <c r="F16" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6" t="n">
+      <c r="A17" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>12</v>
+      <c r="B17" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1928,22 +2174,25 @@
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1951,22 +2200,25 @@
         <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1974,22 +2226,25 @@
         <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1997,22 +2252,25 @@
         <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2020,68 +2278,77 @@
         <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="6" t="n">
+      <c r="A23" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="D23" s="7" t="s">
+      <c r="B23" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="E23" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="F23" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G23" s="6" t="s">
-        <v>12</v>
+      <c r="C23" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="6" t="n">
+      <c r="A24" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="F24" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>12</v>
+      <c r="B24" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2089,22 +2356,25 @@
         <v>24</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2112,22 +2382,25 @@
         <v>25</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2135,22 +2408,25 @@
         <v>26</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2158,22 +2434,25 @@
         <v>27</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2181,22 +2460,25 @@
         <v>28</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2204,22 +2486,25 @@
         <v>29</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2227,206 +2512,233 @@
         <v>30</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6" t="n">
+      <c r="A32" s="7" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="D32" s="7" t="s">
+      <c r="B32" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="E32" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F32" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G32" s="6" t="s">
-        <v>12</v>
+      <c r="C32" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G32" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H32" s="7" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="6" t="n">
+      <c r="A33" s="7" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="C33" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="E33" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F33" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G33" s="6" t="s">
-        <v>12</v>
+      <c r="B33" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G33" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H33" s="7" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="6" t="n">
+      <c r="A34" s="7" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F34" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G34" s="6" t="s">
-        <v>12</v>
+      <c r="B34" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G34" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H34" s="7" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="6" t="n">
+      <c r="A35" s="7" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="C35" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F35" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G35" s="6" t="s">
-        <v>12</v>
+      <c r="B35" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G35" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H35" s="7" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="6" t="n">
+      <c r="A36" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="C36" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F36" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G36" s="6" t="s">
-        <v>12</v>
+      <c r="B36" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G36" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H36" s="7" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="6" t="n">
+      <c r="A37" s="7" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="C37" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="E37" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="F37" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G37" s="6" t="s">
-        <v>12</v>
+      <c r="B37" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G37" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H37" s="7" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="6" t="n">
+      <c r="A38" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="C38" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="D38" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="E38" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="F38" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G38" s="6" t="s">
-        <v>12</v>
+      <c r="B38" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F38" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G38" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H38" s="7" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="6" t="n">
+      <c r="A39" s="7" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="C39" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="D39" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="E39" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="F39" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G39" s="6" t="s">
-        <v>12</v>
+      <c r="B39" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G39" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H39" s="7" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2434,22 +2746,25 @@
         <v>39</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="H40" s="6" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2457,22 +2772,25 @@
         <v>40</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="H41" s="6" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2480,22 +2798,25 @@
         <v>41</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="H42" s="6" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2503,22 +2824,25 @@
         <v>42</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="H43" s="6" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2526,22 +2850,25 @@
         <v>43</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="H44" s="6" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2549,160 +2876,181 @@
         <v>44</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="H45" s="6" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="6" t="n">
+      <c r="A46" s="7" t="n">
         <v>45</v>
       </c>
-      <c r="B46" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="C46" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D46" s="7" t="s">
+      <c r="B46" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="E46" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F46" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G46" s="6" t="s">
-        <v>12</v>
+      <c r="C46" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F46" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G46" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H46" s="10" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="6" t="n">
+      <c r="A47" s="7" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="C47" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="D47" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="E47" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F47" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G47" s="6" t="s">
-        <v>12</v>
+      <c r="B47" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F47" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G47" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H47" s="10" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="6" t="n">
+      <c r="A48" s="7" t="n">
         <v>47</v>
       </c>
-      <c r="B48" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="C48" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="D48" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="E48" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F48" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G48" s="6" t="s">
-        <v>12</v>
+      <c r="B48" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="D48" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F48" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G48" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H48" s="10" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="6" t="n">
+      <c r="A49" s="7" t="n">
         <v>48</v>
       </c>
-      <c r="B49" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="C49" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="D49" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="E49" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F49" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G49" s="6" t="s">
-        <v>12</v>
+      <c r="B49" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E49" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F49" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G49" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H49" s="10" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="6" t="n">
+      <c r="A50" s="7" t="n">
         <v>49</v>
       </c>
-      <c r="B50" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="C50" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="D50" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="E50" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F50" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G50" s="6" t="s">
-        <v>12</v>
+      <c r="B50" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="C50" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="D50" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F50" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G50" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H50" s="10" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="6" t="n">
+      <c r="A51" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="B51" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="C51" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="D51" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="E51" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F51" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G51" s="6" t="s">
-        <v>12</v>
+      <c r="B51" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="C51" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="D51" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="E51" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F51" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G51" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H51" s="10" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2710,22 +3058,25 @@
         <v>51</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2733,39 +3084,43 @@
         <v>52</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="H53" s="6" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="B55" s="9"/>
-      <c r="C55" s="9"/>
-      <c r="D55" s="9"/>
-      <c r="E55" s="9"/>
-      <c r="F55" s="9"/>
-      <c r="G55" s="9"/>
+      <c r="A55" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="B55" s="11"/>
+      <c r="C55" s="11"/>
+      <c r="D55" s="11"/>
+      <c r="E55" s="11"/>
+      <c r="F55" s="11"/>
+      <c r="G55" s="11"/>
+      <c r="H55" s="11"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G53"/>
+  <autoFilter ref="A1:H53"/>
   <mergeCells count="1">
-    <mergeCell ref="A55:G55"/>
+    <mergeCell ref="A55:H55"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2783,7 +3138,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
@@ -2791,191 +3146,209 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="10" t="s">
-        <v>130</v>
+      <c r="A1" s="12" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="11" t="s">
-        <v>131</v>
+      <c r="B3" s="13" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="12" t="n">
+      <c r="A4" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="14" t="n">
         <f aca="false">COUNTIF('고객 프로필 정보'!$E$2:$E$53,A4)</f>
         <v>36</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="B5" s="12" t="n">
+      <c r="A5" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" s="14" t="n">
         <f aca="false">COUNTIF('고객 프로필 정보'!$E$2:$E$53,A5)</f>
         <v>6</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="B6" s="12" t="n">
+      <c r="A6" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" s="14" t="n">
         <f aca="false">COUNTIF('고객 프로필 정보'!$E$2:$E$53,A6)</f>
         <v>3</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7" s="12" t="n">
+      <c r="A7" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="14" t="n">
         <f aca="false">COUNTIF('고객 프로필 정보'!$E$2:$E$53,A7)</f>
         <v>5</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="B8" s="12" t="n">
+      <c r="A8" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="14" t="n">
         <f aca="false">COUNTIF('고객 프로필 정보'!$E$2:$E$53,A8)</f>
         <v>2</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="B9" s="12" t="n">
+      <c r="A9" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="B9" s="14" t="n">
         <f aca="false">SUM(B4:B8)</f>
         <v>52</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="12" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="13" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>131</v>
-      </c>
-    </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="B12" s="12" t="n">
+      <c r="A12" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="14" t="n">
         <f aca="false">COUNTIF('고객 프로필 정보'!$B$2:$B$53,A12)</f>
         <v>7</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" s="12" t="n">
+      <c r="A13" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="14" t="n">
         <f aca="false">COUNTIF('고객 프로필 정보'!$B$2:$B$53,A13)</f>
         <v>3</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14" s="12" t="n">
+      <c r="A14" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="14" t="n">
         <f aca="false">COUNTIF('고객 프로필 정보'!$B$2:$B$53,A14)</f>
         <v>2</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="B15" s="12" t="n">
+      <c r="A15" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" s="14" t="n">
         <f aca="false">COUNTIF('고객 프로필 정보'!$B$2:$B$53,A15)</f>
         <v>4</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="B16" s="12" t="n">
+      <c r="A16" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="B16" s="14" t="n">
         <f aca="false">COUNTIF('고객 프로필 정보'!$B$2:$B$53,A16)</f>
         <v>5</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="B17" s="12" t="n">
+      <c r="A17" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="B17" s="14" t="n">
         <f aca="false">COUNTIF('고객 프로필 정보'!$B$2:$B$53,A17)</f>
         <v>2</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="B18" s="12" t="n">
+      <c r="A18" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="B18" s="14" t="n">
         <f aca="false">COUNTIF('고객 프로필 정보'!$B$2:$B$53,A18)</f>
         <v>7</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="B19" s="12" t="n">
+      <c r="A19" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="B19" s="14" t="n">
         <f aca="false">COUNTIF('고객 프로필 정보'!$B$2:$B$53,A19)</f>
         <v>8</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="B20" s="12" t="n">
+      <c r="A20" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="B20" s="14" t="n">
         <f aca="false">COUNTIF('고객 프로필 정보'!$B$2:$B$53,A20)</f>
         <v>6</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="B21" s="12" t="n">
+      <c r="A21" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="B21" s="14" t="n">
         <f aca="false">COUNTIF('고객 프로필 정보'!$B$2:$B$53,A21)</f>
         <v>6</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="13" t="s">
-        <v>124</v>
-      </c>
-      <c r="B22" s="12" t="n">
+      <c r="A22" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="B22" s="14" t="n">
         <f aca="false">COUNTIF('고객 프로필 정보'!$B$2:$B$53,A22)</f>
         <v>2</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="B23" s="12" t="n">
+      <c r="A23" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="B23" s="14" t="n">
         <f aca="false">SUM(B12:B22)</f>
         <v>52</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="B25" s="14" t="n">
+        <f aca="false">COUNTIF('고객 프로필 정보'!$H$2:$H$53,"O")</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="B26" s="14" t="n">
+        <f aca="false">COUNTIF('고객 프로필 정보'!$H$2:$H$53,"-")</f>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
